--- a/public/exports-with-coowners/29189986.xlsx
+++ b/public/exports-with-coowners/29189986.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -6289,12 +6289,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289829</t>
+          <t xml:space="preserve">311289859</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Rambøll Danmark A/S</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">

--- a/public/exports-with-coowners/29189986.xlsx
+++ b/public/exports-with-coowners/29189986.xlsx
@@ -1279,12 +1279,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gyldigt</t>
+          <t xml:space="preserve">Udløbet</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nej</t>
+          <t xml:space="preserve">Ja</t>
         </is>
       </c>
     </row>
@@ -6289,12 +6289,12 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M84" t="inlineStr">
@@ -6364,12 +6364,12 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t xml:space="preserve">311289859</t>
+          <t xml:space="preserve">311289829</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rambøll Danmark A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M86" t="inlineStr">
